--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-encounter-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
